--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39106-2026 artfynd.xlsx
+++ b/artfynd/A 39106-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480964</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480965</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
